--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0006_ses-01_pet_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0006_ses-01_pet_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -354,7 +355,7 @@
         <v>0</v>
       </c>
       <c r="BG1" s="0">
-        <v>0.018484288354898334</v>
+        <v>0.018484288354898335</v>
       </c>
       <c r="BH1" s="0">
         <v>0.016733601070950468</v>
@@ -821,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="CP2" s="0">
-        <v>0.0039972818483431267</v>
+        <v>0.0039972818483431268</v>
       </c>
       <c r="CQ2" s="0">
         <v>0</v>
@@ -1404,7 +1405,7 @@
         <v>0.055648302726766838</v>
       </c>
       <c r="AU4" s="0">
-        <v>0.092729970326409505</v>
+        <v>0.092729970326409506</v>
       </c>
       <c r="AV4" s="0">
         <v>0.052164840897235269</v>
@@ -1739,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="AL5" s="0">
-        <v>0.058038305281485784</v>
+        <v>0.058038305281485785</v>
       </c>
       <c r="AM5" s="0">
         <v>0.061785603954278658</v>
@@ -1778,7 +1779,7 @@
         <v>0.070900435531246836</v>
       </c>
       <c r="AY5" s="0">
-        <v>0.020222446916076844</v>
+        <v>0.020222446916076845</v>
       </c>
       <c r="AZ5" s="0">
         <v>0.030875632950475487</v>
@@ -1802,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="BG5" s="0">
-        <v>0.018484288354898334</v>
+        <v>0.018484288354898335</v>
       </c>
       <c r="BH5" s="0">
         <v>0</v>
@@ -2128,7 +2129,7 @@
         <v>0.27824151363383415</v>
       </c>
       <c r="AU6" s="0">
-        <v>0.092729970326409505</v>
+        <v>0.092729970326409506</v>
       </c>
       <c r="AV6" s="0">
         <v>0.0447127207690588</v>
@@ -2140,7 +2141,7 @@
         <v>0.091157702825888795</v>
       </c>
       <c r="AY6" s="0">
-        <v>0.020222446916076844</v>
+        <v>0.020222446916076845</v>
       </c>
       <c r="AZ6" s="0">
         <v>0.030875632950475487</v>
@@ -2164,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="BG6" s="0">
-        <v>0.018484288354898334</v>
+        <v>0.018484288354898335</v>
       </c>
       <c r="BH6" s="0">
         <v>0.0055778670236501559</v>
@@ -2493,7 +2494,7 @@
         <v>0.13600395647873395</v>
       </c>
       <c r="AV7" s="0">
-        <v>0.0894254415381176</v>
+        <v>0.089425441538117601</v>
       </c>
       <c r="AW7" s="0">
         <v>0.044851094366702551</v>
@@ -2813,7 +2814,7 @@
         <v>0.13580805794477141</v>
       </c>
       <c r="AH8" s="0">
-        <v>0.047573739295908662</v>
+        <v>0.047573739295908663</v>
       </c>
       <c r="AI8" s="0">
         <v>0.070943549204418768</v>
@@ -2888,13 +2889,13 @@
         <v>0.041649312786339029</v>
       </c>
       <c r="BG8" s="0">
-        <v>0.018484288354898334</v>
+        <v>0.018484288354898335</v>
       </c>
       <c r="BH8" s="0">
         <v>0</v>
       </c>
       <c r="BI8" s="0">
-        <v>0.046620046620046623</v>
+        <v>0.046620046620046624</v>
       </c>
       <c r="BJ8" s="0">
         <v>0.0073705546342362266</v>
@@ -2954,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="CC8" s="0">
-        <v>0.21247344081989752</v>
+        <v>0.21247344081989753</v>
       </c>
       <c r="CD8" s="0">
         <v>0</v>
@@ -3112,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N9" s="0">
         <v>0</v>
@@ -3142,7 +3143,7 @@
         <v>0.030637254901960755</v>
       </c>
       <c r="W9" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X9" s="0">
         <v>0</v>
@@ -3280,7 +3281,7 @@
         <v>0.03674309229864782</v>
       </c>
       <c r="BQ9" s="0">
-        <v>0.35893754486719281</v>
+        <v>0.35893754486719282</v>
       </c>
       <c r="BR9" s="0">
         <v>0</v>
@@ -3528,7 +3529,7 @@
         <v>0.071377587437544687</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.068306010928961824</v>
+        <v>0.068306010928961825</v>
       </c>
       <c r="AF10" s="0">
         <v>0</v>
@@ -3690,7 +3691,7 @@
         <v>0.057570523891767471</v>
       </c>
       <c r="CG10" s="0">
-        <v>0.0059091177687171361</v>
+        <v>0.0059091177687171362</v>
       </c>
       <c r="CH10" s="0">
         <v>0.0044167660439026583</v>
@@ -3965,7 +3966,7 @@
         <v>0.39360081259522567</v>
       </c>
       <c r="BD11" s="0">
-        <v>0.020554984583761544</v>
+        <v>0.020554984583761545</v>
       </c>
       <c r="BE11" s="0">
         <v>0.062509767151117307</v>
@@ -4037,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="CB11" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC11" s="0">
         <v>0.29996250468691388</v>
@@ -4168,13 +4169,13 @@
         <v>0.01672520488375984</v>
       </c>
       <c r="C12" s="0">
-        <v>0.035351303579319523</v>
+        <v>0.035351303579319524</v>
       </c>
       <c r="D12" s="0">
         <v>0.0027320165013796712</v>
       </c>
       <c r="E12" s="0">
-        <v>0.01868984207083452</v>
+        <v>0.018689842070834521</v>
       </c>
       <c r="F12" s="0">
         <v>0.0057387162491750647</v>
@@ -4261,7 +4262,7 @@
         <v>0.23389165534932871</v>
       </c>
       <c r="AH12" s="0">
-        <v>0.063431652394544943</v>
+        <v>0.063431652394544944</v>
       </c>
       <c r="AI12" s="0">
         <v>0.22296544035674493</v>
@@ -4324,7 +4325,7 @@
         <v>0.088704908338261473</v>
       </c>
       <c r="BC12" s="0">
-        <v>0.46978161503301213</v>
+        <v>0.46978161503301214</v>
       </c>
       <c r="BD12" s="0">
         <v>0.041109969167523165</v>
@@ -4390,7 +4391,7 @@
         <v>0.084139671855279846</v>
       </c>
       <c r="BY12" s="0">
-        <v>0.069676700111482789</v>
+        <v>0.06967670011148279</v>
       </c>
       <c r="BZ12" s="0">
         <v>0.19747235387045831</v>
@@ -4426,7 +4427,7 @@
         <v>0.43221589711153319</v>
       </c>
       <c r="CK12" s="0">
-        <v>0.17312331488576715</v>
+        <v>0.17312331488576716</v>
       </c>
       <c r="CL12" s="0">
         <v>0.32209170140204652</v>
@@ -4560,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N13" s="0">
         <v>0.031152647975077854</v>
@@ -4596,7 +4597,7 @@
         <v>0.03790032215273826</v>
       </c>
       <c r="Y13" s="0">
-        <v>0.44549266247379415</v>
+        <v>0.44549266247379416</v>
       </c>
       <c r="Z13" s="0">
         <v>0</v>
@@ -4973,7 +4974,7 @@
         <v>0.094562647754137211</v>
       </c>
       <c r="AD14" s="0">
-        <v>0.095170116583392902</v>
+        <v>0.095170116583392903</v>
       </c>
       <c r="AE14" s="0">
         <v>0</v>
@@ -5356,7 +5357,7 @@
         <v>0.051599587203302329</v>
       </c>
       <c r="AK15" s="0">
-        <v>0.059430948666518039</v>
+        <v>0.05943094866651804</v>
       </c>
       <c r="AL15" s="0">
         <v>0.50299864577287634</v>
@@ -5664,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="0">
-        <v>0.037150552614470179</v>
+        <v>0.03715055261447018</v>
       </c>
       <c r="T16" s="0">
         <v>0.040975209997951276</v>
@@ -5697,7 +5698,7 @@
         <v>0.094562647754137211</v>
       </c>
       <c r="AD16" s="0">
-        <v>0.21413276231263403</v>
+        <v>0.21413276231263404</v>
       </c>
       <c r="AE16" s="0">
         <v>0.13661202185792365</v>
@@ -5823,7 +5824,7 @@
         <v>0.25041399087200639</v>
       </c>
       <c r="BT16" s="0">
-        <v>0.29678622911896912</v>
+        <v>0.29678622911896913</v>
       </c>
       <c r="BU16" s="0">
         <v>0.02072324111491039</v>
@@ -5838,7 +5839,7 @@
         <v>0.23839573692329288</v>
       </c>
       <c r="BY16" s="0">
-        <v>0.25083612040133801</v>
+        <v>0.25083612040133802</v>
       </c>
       <c r="BZ16" s="0">
         <v>0.34228541337546109</v>
@@ -5889,7 +5890,7 @@
         <v>0.0088160098739310678</v>
       </c>
       <c r="CP16" s="0">
-        <v>0.14789942838869582</v>
+        <v>0.14789942838869583</v>
       </c>
       <c r="CQ16" s="0">
         <v>0</v>
@@ -6011,7 +6012,7 @@
         <v>0.13860013860013848</v>
       </c>
       <c r="N17" s="0">
-        <v>0.041536863966770476</v>
+        <v>0.041536863966770477</v>
       </c>
       <c r="O17" s="0">
         <v>0.05932370970931377</v>
@@ -6080,7 +6081,7 @@
         <v>0.16511867905056746</v>
       </c>
       <c r="AK17" s="0">
-        <v>0.059430948666518039</v>
+        <v>0.05943094866651804</v>
       </c>
       <c r="AL17" s="0">
         <v>0.62552395692267948</v>
@@ -6397,7 +6398,7 @@
         <v>0.52054285183119497</v>
       </c>
       <c r="V18" s="0">
-        <v>0.29105392156862719</v>
+        <v>0.2910539215686272</v>
       </c>
       <c r="W18" s="0">
         <v>0.42735042735042694</v>
@@ -6490,7 +6491,7 @@
         <v>0.45078424107694165</v>
       </c>
       <c r="BA18" s="0">
-        <v>0.220195029883611</v>
+        <v>0.22019502988361101</v>
       </c>
       <c r="BB18" s="0">
         <v>0.34496353242657174</v>
@@ -6568,7 +6569,7 @@
         <v>0.55292259083728235</v>
       </c>
       <c r="CA18" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB18" s="0">
         <v>0.15748031496062978</v>
@@ -6813,7 +6814,7 @@
         <v>1.2974976830398555</v>
       </c>
       <c r="AN19" s="0">
-        <v>0.99956540634507018</v>
+        <v>0.99956540634507019</v>
       </c>
       <c r="AO19" s="0">
         <v>0.22471910112359614</v>
@@ -6840,7 +6841,7 @@
         <v>0.65578657127953088</v>
       </c>
       <c r="AW19" s="0">
-        <v>0.53821313240043211</v>
+        <v>0.53821313240043212</v>
       </c>
       <c r="AX19" s="0">
         <v>0.79003342449103831</v>
@@ -6852,7 +6853,7 @@
         <v>0.61133753241941624</v>
       </c>
       <c r="BA19" s="0">
-        <v>0.35650623885918103</v>
+        <v>0.35650623885918104</v>
       </c>
       <c r="BB19" s="0">
         <v>0.37453183520599354</v>
@@ -6927,7 +6928,7 @@
         <v>0.22296544035674531</v>
       </c>
       <c r="BZ19" s="0">
-        <v>0.55292259083728434</v>
+        <v>0.55292259083728435</v>
       </c>
       <c r="CA19" s="0">
         <v>0.10025062656641633</v>
@@ -7085,7 +7086,7 @@
         <v>0.04983388704318932</v>
       </c>
       <c r="J20" s="0">
-        <v>0.044759895133959927</v>
+        <v>0.044759895133959928</v>
       </c>
       <c r="K20" s="0">
         <v>0.24705435195743042</v>
@@ -7136,7 +7137,7 @@
         <v>0.16014641958361917</v>
       </c>
       <c r="AA20" s="0">
-        <v>0.23453532688361164</v>
+        <v>0.23453532688361165</v>
       </c>
       <c r="AB20" s="0">
         <v>0.16349887594522772</v>
@@ -7232,7 +7233,7 @@
         <v>0.34707760655282488</v>
       </c>
       <c r="BG20" s="0">
-        <v>0.48059149722735633</v>
+        <v>0.48059149722735634</v>
       </c>
       <c r="BH20" s="0">
         <v>0.20638107987505558</v>
@@ -7244,7 +7245,7 @@
         <v>0.17320803390455117</v>
       </c>
       <c r="BK20" s="0">
-        <v>0.57696270348238154</v>
+        <v>0.57696270348238155</v>
       </c>
       <c r="BL20" s="0">
         <v>0.42032862055789039</v>
@@ -7325,16 +7326,16 @@
         <v>0.55626507733787378</v>
       </c>
       <c r="CL20" s="0">
-        <v>0.92838196286472074</v>
+        <v>0.92838196286472075</v>
       </c>
       <c r="CM20" s="0">
         <v>0.093161915408980722</v>
       </c>
       <c r="CN20" s="0">
-        <v>0.35893754486719281</v>
+        <v>0.35893754486719282</v>
       </c>
       <c r="CO20" s="0">
-        <v>0.13224014810896575</v>
+        <v>0.13224014810896576</v>
       </c>
       <c r="CP20" s="0">
         <v>0.26781788383898925</v>
@@ -7486,7 +7487,7 @@
         <v>0.32169117647058798</v>
       </c>
       <c r="W21" s="0">
-        <v>0.75213675213675157</v>
+        <v>0.75213675213675158</v>
       </c>
       <c r="X21" s="0">
         <v>0.075800644305476519</v>
@@ -7516,7 +7517,7 @@
         <v>0.63157894736842057</v>
       </c>
       <c r="AG21" s="0">
-        <v>0.746944318696242</v>
+        <v>0.74694431869624201</v>
       </c>
       <c r="AH21" s="0">
         <v>0.46780843640976805</v>
@@ -7771,7 +7772,7 @@
         <v>0.28490028490028468</v>
       </c>
       <c r="DN21" s="0">
-        <v>0.7161458333333327</v>
+        <v>0.71614583333333271</v>
       </c>
       <c r="DO21" s="0">
         <v>0</v>
@@ -7797,7 +7798,7 @@
         <v>0.23362302588543105</v>
       </c>
       <c r="F22" s="0">
-        <v>0.068864594990100655</v>
+        <v>0.068864594990100656</v>
       </c>
       <c r="G22" s="0">
         <v>0.20032051282051266</v>
@@ -7845,7 +7846,7 @@
         <v>0.92954080684141949</v>
       </c>
       <c r="V22" s="0">
-        <v>0.49019607843137208</v>
+        <v>0.49019607843137209</v>
       </c>
       <c r="W22" s="0">
         <v>0.88888888888888817</v>
@@ -7869,7 +7870,7 @@
         <v>0.30732860520094535</v>
       </c>
       <c r="AD22" s="0">
-        <v>0.54722817035450821</v>
+        <v>0.54722817035450822</v>
       </c>
       <c r="AE22" s="0">
         <v>0.6147540983606552</v>
@@ -8162,13 +8163,13 @@
         <v>0.14920662247855196</v>
       </c>
       <c r="G23" s="0">
-        <v>0.16025641025641071</v>
+        <v>0.16025641025641072</v>
       </c>
       <c r="H23" s="0">
         <v>0.11101019275406228</v>
       </c>
       <c r="I23" s="0">
-        <v>0.088593576965670245</v>
+        <v>0.088593576965670246</v>
       </c>
       <c r="J23" s="0">
         <v>0.057548436600805837</v>
@@ -8195,7 +8196,7 @@
         <v>0.10288065843621427</v>
       </c>
       <c r="R23" s="0">
-        <v>0.045913682277318769</v>
+        <v>0.04591368227731877</v>
       </c>
       <c r="S23" s="0">
         <v>0.13002693415064587</v>
@@ -8237,7 +8238,7 @@
         <v>0.20491803278688581</v>
       </c>
       <c r="AF23" s="0">
-        <v>0.6315789473684229</v>
+        <v>0.63157894736842291</v>
       </c>
       <c r="AG23" s="0">
         <v>1.0713746793420884</v>
@@ -8255,7 +8256,7 @@
         <v>0.30458361191590605</v>
       </c>
       <c r="AL23" s="0">
-        <v>1.2123557103243729</v>
+        <v>1.212355710324373</v>
       </c>
       <c r="AM23" s="0">
         <v>1.0812480691998794</v>
@@ -8360,7 +8361,7 @@
         <v>0.78012380225557754</v>
       </c>
       <c r="BU23" s="0">
-        <v>0.23831727282146994</v>
+        <v>0.23831727282146995</v>
       </c>
       <c r="BV23" s="0">
         <v>0.68796068796068988</v>
@@ -8393,7 +8394,7 @@
         <v>0.76190476190476408</v>
       </c>
       <c r="CF23" s="0">
-        <v>0.69084628670121095</v>
+        <v>0.69084628670121096</v>
       </c>
       <c r="CG23" s="0">
         <v>0.20681912190510016</v>
@@ -8408,7 +8409,7 @@
         <v>1.2650221378874165</v>
       </c>
       <c r="CK23" s="0">
-        <v>0.77479778629204143</v>
+        <v>0.77479778629204144</v>
       </c>
       <c r="CL23" s="0">
         <v>1.1525830491347764</v>
@@ -8629,7 +8630,7 @@
         <v>0.50936329588014939</v>
       </c>
       <c r="AP24" s="0">
-        <v>0.85356880058866746</v>
+        <v>0.85356880058866747</v>
       </c>
       <c r="AQ24" s="0">
         <v>0.37195994277539307</v>
@@ -8656,7 +8657,7 @@
         <v>1.1951787703838741</v>
       </c>
       <c r="AY24" s="0">
-        <v>0.64037748567576624</v>
+        <v>0.64037748567576625</v>
       </c>
       <c r="AZ24" s="0">
         <v>0.79659133012226679</v>
@@ -8689,7 +8690,7 @@
         <v>0.81047157970234829</v>
       </c>
       <c r="BJ24" s="0">
-        <v>0.39432467293163775</v>
+        <v>0.39432467293163776</v>
       </c>
       <c r="BK24" s="0">
         <v>0.82423243354625941</v>
@@ -8871,7 +8872,7 @@
         <v>0.32604757879483126</v>
       </c>
       <c r="B25" s="0">
-        <v>0.17561465127947803</v>
+        <v>0.17561465127947804</v>
       </c>
       <c r="C25" s="0">
         <v>0.30637796435410197</v>
@@ -8904,7 +8905,7 @@
         <v>0.14207068016338115</v>
       </c>
       <c r="M25" s="0">
-        <v>0.44352044352044317</v>
+        <v>0.44352044352044318</v>
       </c>
       <c r="N25" s="0">
         <v>0.20768431983385235</v>
@@ -9015,7 +9016,7 @@
         <v>0.95084320057409311</v>
       </c>
       <c r="AX25" s="0">
-        <v>1.2255646713258372</v>
+        <v>1.2255646713258373</v>
       </c>
       <c r="AY25" s="0">
         <v>0.72126727334007357</v>
@@ -9027,7 +9028,7 @@
         <v>0.71301247771835941</v>
       </c>
       <c r="BB25" s="0">
-        <v>0.70963926670609045</v>
+        <v>0.70963926670609046</v>
       </c>
       <c r="BC25" s="0">
         <v>1.2908413746402561</v>
@@ -9117,7 +9118,7 @@
         <v>0.95238095238095155</v>
       </c>
       <c r="CF25" s="0">
-        <v>0.80598733448474313</v>
+        <v>0.80598733448474314</v>
       </c>
       <c r="CG25" s="0">
         <v>0.3013650062045734</v>
@@ -9126,10 +9127,10 @@
         <v>0.21642153615122989</v>
       </c>
       <c r="CI25" s="0">
-        <v>0.79866888519134704</v>
+        <v>0.79866888519134705</v>
       </c>
       <c r="CJ25" s="0">
-        <v>1.3388150959308442</v>
+        <v>1.3388150959308443</v>
       </c>
       <c r="CK25" s="0">
         <v>0.89683553285085782</v>
@@ -9141,7 +9142,7 @@
         <v>0.2049562138997576</v>
       </c>
       <c r="CN25" s="0">
-        <v>0.93323761665470117</v>
+        <v>0.93323761665470118</v>
       </c>
       <c r="CO25" s="0">
         <v>0.19395221722648312</v>
@@ -9156,7 +9157,7 @@
         <v>0.11718333865984863</v>
       </c>
       <c r="CS25" s="0">
-        <v>1.7838714433141662</v>
+        <v>1.7838714433141663</v>
       </c>
       <c r="CT25" s="0">
         <v>0</v>
@@ -9192,7 +9193,7 @@
         <v>0.26715239829993903</v>
       </c>
       <c r="DE25" s="0">
-        <v>0.096665055582406872</v>
+        <v>0.096665055582406873</v>
       </c>
       <c r="DF25" s="0">
         <v>0</v>
@@ -9266,7 +9267,7 @@
         <v>0.30190019534718493</v>
       </c>
       <c r="M26" s="0">
-        <v>0.44352044352044317</v>
+        <v>0.44352044352044318</v>
       </c>
       <c r="N26" s="0">
         <v>0.24922118380062283</v>
@@ -9317,7 +9318,7 @@
         <v>0.68557919621749341</v>
       </c>
       <c r="AD26" s="0">
-        <v>1.0706638115631681</v>
+        <v>1.0706638115631682</v>
       </c>
       <c r="AE26" s="0">
         <v>0.54644808743169349</v>
@@ -9341,7 +9342,7 @@
         <v>0.46801872074882955</v>
       </c>
       <c r="AL26" s="0">
-        <v>1.2832914167795177</v>
+        <v>1.2832914167795178</v>
       </c>
       <c r="AM26" s="0">
         <v>1.4519616929255472</v>
@@ -9398,13 +9399,13 @@
         <v>0.47276464542651553</v>
       </c>
       <c r="BE26" s="0">
-        <v>0.90639162369120096</v>
+        <v>0.90639162369120097</v>
       </c>
       <c r="BF26" s="0">
         <v>0.76357073441621481</v>
       </c>
       <c r="BG26" s="0">
-        <v>0.97350585335797823</v>
+        <v>0.97350585335797824</v>
       </c>
       <c r="BH26" s="0">
         <v>0.79763498438197156</v>
@@ -9619,7 +9620,7 @@
         <v>0.22702104097452916</v>
       </c>
       <c r="J27" s="0">
-        <v>0.31971353667114238</v>
+        <v>0.31971353667114239</v>
       </c>
       <c r="K27" s="0">
         <v>0.62713797035347718</v>
@@ -9679,7 +9680,7 @@
         <v>0.52009456264775367</v>
       </c>
       <c r="AD27" s="0">
-        <v>0.80894599095883823</v>
+        <v>0.80894599095883824</v>
       </c>
       <c r="AE27" s="0">
         <v>1.0245901639344253</v>
@@ -9703,7 +9704,7 @@
         <v>0.6834559096649574</v>
       </c>
       <c r="AL27" s="0">
-        <v>1.3671245244083305</v>
+        <v>1.3671245244083306</v>
       </c>
       <c r="AM27" s="0">
         <v>1.5446400988569648</v>
@@ -9715,7 +9716,7 @@
         <v>0.77902621722846377</v>
       </c>
       <c r="AP27" s="0">
-        <v>1.0448859455481962</v>
+        <v>1.0448859455481963</v>
       </c>
       <c r="AQ27" s="0">
         <v>0.57224606580829707</v>
@@ -9808,10 +9809,10 @@
         <v>1.1574662935639777</v>
       </c>
       <c r="BU27" s="0">
-        <v>0.34193347839602078</v>
+        <v>0.34193347839602079</v>
       </c>
       <c r="BV27" s="0">
-        <v>0.93366093366093283</v>
+        <v>0.93366093366093284</v>
       </c>
       <c r="BW27" s="0">
         <v>0.89181286549707528</v>
@@ -9978,7 +9979,7 @@
         <v>0.33303057826218685</v>
       </c>
       <c r="I28" s="0">
-        <v>0.28239202657807388</v>
+        <v>0.28239202657807389</v>
       </c>
       <c r="J28" s="0">
         <v>0.31331926593772069</v>
@@ -10140,7 +10141,7 @@
         <v>0.70388796756956151</v>
       </c>
       <c r="BK28" s="0">
-        <v>1.0715021636101409</v>
+        <v>1.071502163610141</v>
       </c>
       <c r="BL28" s="0">
         <v>1.0699273977837249</v>
@@ -10200,7 +10201,7 @@
         <v>0.55128205128205288</v>
       </c>
       <c r="CE28" s="0">
-        <v>1.3968253968254007</v>
+        <v>1.3968253968254008</v>
       </c>
       <c r="CF28" s="0">
         <v>1.3816925734024219</v>
@@ -10227,7 +10228,7 @@
         <v>0.46580957704490539</v>
       </c>
       <c r="CN28" s="0">
-        <v>1.2323522373773665</v>
+        <v>1.2323522373773666</v>
       </c>
       <c r="CO28" s="0">
         <v>0.37027241470510552</v>
@@ -10340,7 +10341,7 @@
         <v>0.40367342819658858</v>
       </c>
       <c r="I29" s="0">
-        <v>0.24916943521594664</v>
+        <v>0.24916943521594665</v>
       </c>
       <c r="J29" s="0">
         <v>0.34529061960483376</v>
@@ -10487,7 +10488,7 @@
         <v>1.3127051101734635</v>
       </c>
       <c r="BF29" s="0">
-        <v>0.93016798556157076</v>
+        <v>0.93016798556157077</v>
       </c>
       <c r="BG29" s="0">
         <v>1.0536044362292043</v>
@@ -10526,7 +10527,7 @@
         <v>0.6458383789456682</v>
       </c>
       <c r="BS29" s="0">
-        <v>1.1712912476271244</v>
+        <v>1.1712912476271245</v>
       </c>
       <c r="BT29" s="0">
         <v>1.1362672771983369</v>
@@ -10658,7 +10659,7 @@
         <v>0.27100271002710008</v>
       </c>
       <c r="DK29" s="0">
-        <v>3.6292186777623638</v>
+        <v>3.6292186777623639</v>
       </c>
       <c r="DL29" s="0">
         <v>1.8276762402088758</v>
@@ -10673,7 +10674,7 @@
         <v>1.9417475728155322</v>
       </c>
       <c r="DP29" s="0">
-        <v>2.9342723004694808</v>
+        <v>2.9342723004694809</v>
       </c>
     </row>
     <row r="30">
@@ -10684,7 +10685,7 @@
         <v>0.43903662819869504</v>
       </c>
       <c r="C30" s="0">
-        <v>0.57151274119899786</v>
+        <v>0.57151274119899787</v>
       </c>
       <c r="D30" s="0">
         <v>0.51908313526213656</v>
@@ -10864,7 +10865,7 @@
         <v>0.84024322830292908</v>
       </c>
       <c r="BK30" s="0">
-        <v>1.3874579298028697</v>
+        <v>1.3874579298028698</v>
       </c>
       <c r="BL30" s="0">
         <v>1.222774168895681</v>
@@ -10900,7 +10901,7 @@
         <v>0.91728091728091643</v>
       </c>
       <c r="BW30" s="0">
-        <v>1.4619883040935659</v>
+        <v>1.461988304093566</v>
       </c>
       <c r="BX30" s="0">
         <v>1.2200252419015554</v>
@@ -10930,7 +10931,7 @@
         <v>1.1514104778353473</v>
       </c>
       <c r="CG30" s="0">
-        <v>0.70318501447733794</v>
+        <v>0.70318501447733795</v>
       </c>
       <c r="CH30" s="0">
         <v>0.53884545735612344</v>
@@ -11256,7 +11257,7 @@
         <v>1.3058594081234618</v>
       </c>
       <c r="BU31" s="0">
-        <v>0.80820640348150385</v>
+        <v>0.80820640348150386</v>
       </c>
       <c r="BV31" s="0">
         <v>1.2940212940212927</v>
@@ -11295,7 +11296,7 @@
         <v>0.89818590084500305</v>
       </c>
       <c r="CH31" s="0">
-        <v>0.47701073274148625</v>
+        <v>0.47701073274148626</v>
       </c>
       <c r="CI31" s="0">
         <v>1.1092623405435376</v>
@@ -11397,7 +11398,7 @@
         <v>2.1035598705501601</v>
       </c>
       <c r="DP31" s="0">
-        <v>2.9342723004694808</v>
+        <v>2.9342723004694809</v>
       </c>
     </row>
     <row r="32">
@@ -11408,7 +11409,7 @@
         <v>0.5853821709315955</v>
       </c>
       <c r="C32" s="0">
-        <v>0.83959346000884016</v>
+        <v>0.83959346000884017</v>
       </c>
       <c r="D32" s="0">
         <v>0.57099144878835228</v>
@@ -11438,7 +11439,7 @@
         <v>0.78138874089859933</v>
       </c>
       <c r="M32" s="0">
-        <v>1.0117810117810146</v>
+        <v>1.0117810117810147</v>
       </c>
       <c r="N32" s="0">
         <v>0.72689511941848595</v>
@@ -11465,7 +11466,7 @@
         <v>1.3199479457148207</v>
       </c>
       <c r="V32" s="0">
-        <v>0.96507352941176749</v>
+        <v>0.9650735294117675</v>
       </c>
       <c r="W32" s="0">
         <v>1.3846153846153886</v>
@@ -11594,7 +11595,7 @@
         <v>1.2355113998216822</v>
       </c>
       <c r="BM32" s="0">
-        <v>0.92705255229156069</v>
+        <v>0.9270525522915607</v>
       </c>
       <c r="BN32" s="0">
         <v>1.0452240505019175</v>
@@ -11648,7 +11649,7 @@
         <v>0.74358974358974561</v>
       </c>
       <c r="CE32" s="0">
-        <v>1.3968253968254007</v>
+        <v>1.3968253968254008</v>
       </c>
       <c r="CF32" s="0">
         <v>1.7271157167530271</v>
@@ -11672,7 +11673,7 @@
         <v>1.3136288998358001</v>
       </c>
       <c r="CM32" s="0">
-        <v>0.93161915408981077</v>
+        <v>0.93161915408981078</v>
       </c>
       <c r="CN32" s="0">
         <v>1.196458482890647</v>
@@ -11788,7 +11789,7 @@
         <v>0.66606115652437115</v>
       </c>
       <c r="I33" s="0">
-        <v>0.59246954595791756</v>
+        <v>0.59246954595791757</v>
       </c>
       <c r="J33" s="0">
         <v>0.76731248801074159</v>
@@ -11917,7 +11918,7 @@
         <v>1.4627569935962239</v>
       </c>
       <c r="AZ33" s="0">
-        <v>1.3708781030011103</v>
+        <v>1.3708781030011104</v>
       </c>
       <c r="BA33" s="0">
         <v>1.1009751494180551</v>
@@ -11941,7 +11942,7 @@
         <v>1.2692544670363513</v>
       </c>
       <c r="BH33" s="0">
-        <v>1.2717536813922345</v>
+        <v>1.2717536813922346</v>
       </c>
       <c r="BI33" s="0">
         <v>1.3734982965752183</v>
@@ -11983,7 +11984,7 @@
         <v>0.91182260905605561</v>
       </c>
       <c r="BV33" s="0">
-        <v>1.3267813267813255</v>
+        <v>1.3267813267813256</v>
       </c>
       <c r="BW33" s="0">
         <v>1.2573099415204667</v>
@@ -11995,7 +11996,7 @@
         <v>1.2402452619843913</v>
       </c>
       <c r="BZ33" s="0">
-        <v>1.4744602422327528</v>
+        <v>1.4744602422327529</v>
       </c>
       <c r="CA33" s="0">
         <v>1.0025062656641595</v>
@@ -12112,7 +12113,7 @@
         <v>3.6118363794603972</v>
       </c>
       <c r="DM33" s="0">
-        <v>0.85470085470085388</v>
+        <v>0.85470085470085389</v>
       </c>
       <c r="DN33" s="0">
         <v>0.32552083333333304</v>
@@ -12192,7 +12193,7 @@
         <v>1.4859068627450969</v>
       </c>
       <c r="W34" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="X34" s="0">
         <v>0.75800644305476528</v>
@@ -12294,7 +12295,7 @@
         <v>1.2675573826652953</v>
       </c>
       <c r="BE34" s="0">
-        <v>1.2970776683856839</v>
+        <v>1.297077668385684</v>
       </c>
       <c r="BF34" s="0">
         <v>1.1800638622796047</v>
@@ -12318,7 +12319,7 @@
         <v>1.203668322506686</v>
       </c>
       <c r="BM34" s="0">
-        <v>1.2225505533344911</v>
+        <v>1.2225505533344912</v>
       </c>
       <c r="BN34" s="0">
         <v>0.93138776777398236</v>
@@ -12348,7 +12349,7 @@
         <v>1.0974610974610965</v>
       </c>
       <c r="BW34" s="0">
-        <v>1.3596491228070164</v>
+        <v>1.3596491228070165</v>
       </c>
       <c r="BX34" s="0">
         <v>1.3742813069695683</v>
@@ -12366,7 +12367,7 @@
         <v>1.1548556430446184</v>
       </c>
       <c r="CC34" s="0">
-        <v>1.2123484564429436</v>
+        <v>1.2123484564429437</v>
       </c>
       <c r="CD34" s="0">
         <v>0.9487179487179479</v>
@@ -12375,7 +12376,7 @@
         <v>1.1428571428571419</v>
       </c>
       <c r="CF34" s="0">
-        <v>1.4968336211859516</v>
+        <v>1.4968336211859517</v>
       </c>
       <c r="CG34" s="0">
         <v>1.0813685516752338</v>
@@ -12468,13 +12469,13 @@
         <v>2.7100271002710001</v>
       </c>
       <c r="DK34" s="0">
-        <v>2.1729079981507144</v>
+        <v>2.1729079981507145</v>
       </c>
       <c r="DL34" s="0">
         <v>3.872932985204522</v>
       </c>
       <c r="DM34" s="0">
-        <v>0.85470085470085388</v>
+        <v>0.85470085470085389</v>
       </c>
       <c r="DN34" s="0">
         <v>0.32552083333333304</v>
@@ -12497,7 +12498,7 @@
         <v>0.96626896450139843</v>
       </c>
       <c r="D35" s="0">
-        <v>0.75676857088216753</v>
+        <v>0.75676857088216754</v>
       </c>
       <c r="E35" s="0">
         <v>1.1369653926424312</v>
@@ -12530,7 +12531,7 @@
         <v>0.91381100726895037</v>
       </c>
       <c r="O35" s="0">
-        <v>0.98213697185419468</v>
+        <v>0.98213697185419469</v>
       </c>
       <c r="P35" s="0">
         <v>1.0862765170903703</v>
@@ -12557,7 +12558,7 @@
         <v>1.3504273504273492</v>
       </c>
       <c r="X35" s="0">
-        <v>0.83380708736024189</v>
+        <v>0.8338070873602419</v>
       </c>
       <c r="Y35" s="0">
         <v>0.86477987421383573</v>
@@ -12689,7 +12690,7 @@
         <v>1.2045480130586503</v>
       </c>
       <c r="BP35" s="0">
-        <v>1.1537330981775415</v>
+        <v>1.1537330981775416</v>
       </c>
       <c r="BQ35" s="0">
         <v>0.88537927733907562</v>
@@ -12716,7 +12717,7 @@
         <v>1.3181881923993819</v>
       </c>
       <c r="BY35" s="0">
-        <v>1.4492753623188392</v>
+        <v>1.4492753623188393</v>
       </c>
       <c r="BZ35" s="0">
         <v>1.1190100052659284</v>
@@ -12886,7 +12887,7 @@
         <v>0.95897709110282281</v>
       </c>
       <c r="M36" s="0">
-        <v>1.2889812889812879</v>
+        <v>1.288981288981288</v>
       </c>
       <c r="N36" s="0">
         <v>0.89304257528556519</v>
@@ -12904,7 +12905,7 @@
         <v>0.82644628099173478</v>
       </c>
       <c r="S36" s="0">
-        <v>1.0727222067428241</v>
+        <v>1.0727222067428242</v>
       </c>
       <c r="T36" s="0">
         <v>1.119989073277333</v>
@@ -12913,7 +12914,7 @@
         <v>1.2269938650306738</v>
       </c>
       <c r="V36" s="0">
-        <v>1.2254901960784303</v>
+        <v>1.2254901960784304</v>
       </c>
       <c r="W36" s="0">
         <v>1.2136752136752125</v>
@@ -12955,7 +12956,7 @@
         <v>1.2972534711665136</v>
       </c>
       <c r="AJ36" s="0">
-        <v>1.176470588235293</v>
+        <v>1.1764705882352931</v>
       </c>
       <c r="AK36" s="0">
         <v>1.1811901047470459</v>
@@ -13024,7 +13025,7 @@
         <v>1.3744273219491865</v>
       </c>
       <c r="BG36" s="0">
-        <v>1.3062230437461479</v>
+        <v>1.306223043746148</v>
       </c>
       <c r="BH36" s="0">
         <v>1.3833110218652376</v>
@@ -13072,7 +13073,7 @@
         <v>1.1793611793611785</v>
       </c>
       <c r="BW36" s="0">
-        <v>1.5204678362573087</v>
+        <v>1.5204678362573088</v>
       </c>
       <c r="BX36" s="0">
         <v>1.2620950778291953</v>
@@ -13099,7 +13100,7 @@
         <v>0.95238095238095155</v>
       </c>
       <c r="CF36" s="0">
-        <v>0.80598733448474313</v>
+        <v>0.80598733448474314</v>
       </c>
       <c r="CG36" s="0">
         <v>1.0400047272942141</v>
@@ -13365,13 +13366,13 @@
         <v>1.4088304684866857</v>
       </c>
       <c r="AZ37" s="0">
-        <v>1.3708781030011103</v>
+        <v>1.3708781030011104</v>
       </c>
       <c r="BA37" s="0">
         <v>1.2477718360071288</v>
       </c>
       <c r="BB37" s="0">
-        <v>1.1038833037650297</v>
+        <v>1.1038833037650298</v>
       </c>
       <c r="BC37" s="0">
         <v>0.80413069239884805</v>
@@ -13428,7 +13429,7 @@
         <v>1.2761807852115652</v>
       </c>
       <c r="BU37" s="0">
-        <v>1.1397782613200695</v>
+        <v>1.1397782613200696</v>
       </c>
       <c r="BV37" s="0">
         <v>1.4414414414414403</v>
@@ -13524,7 +13525,7 @@
         <v>0.91664724617416216</v>
       </c>
       <c r="DA37" s="0">
-        <v>2.0893371757925054</v>
+        <v>2.0893371757925055</v>
       </c>
       <c r="DB37" s="0">
         <v>1.9331243469174486</v>
@@ -13664,7 +13665,7 @@
         <v>0.99928622412563106</v>
       </c>
       <c r="AE38" s="0">
-        <v>1.8442622950819791</v>
+        <v>1.8442622950819792</v>
       </c>
       <c r="AF38" s="0">
         <v>1.6842105263158005</v>
@@ -13742,7 +13743,7 @@
         <v>1.3018156903049076</v>
       </c>
       <c r="BE38" s="0">
-        <v>1.4064697609001497</v>
+        <v>1.4064697609001498</v>
       </c>
       <c r="BF38" s="0">
         <v>1.4299597389976491</v>
@@ -13820,7 +13821,7 @@
         <v>1.3333333333333421</v>
       </c>
       <c r="CE38" s="0">
-        <v>1.1428571428571503</v>
+        <v>1.1428571428571504</v>
       </c>
       <c r="CF38" s="0">
         <v>0.9786989061600524</v>
@@ -13835,7 +13836,7 @@
         <v>1.2090959511924648</v>
       </c>
       <c r="CJ38" s="0">
-        <v>0.66413662239089621</v>
+        <v>0.66413662239089622</v>
       </c>
       <c r="CK38" s="0">
         <v>1.2232155527174764</v>
@@ -13919,7 +13920,7 @@
         <v>0.43920480813684981</v>
       </c>
       <c r="DL38" s="0">
-        <v>1.5230635335074076</v>
+        <v>1.5230635335074077</v>
       </c>
       <c r="DM38" s="0">
         <v>0.071225071225071698</v>
@@ -13990,7 +13991,7 @@
         <v>1.4692378328741953</v>
       </c>
       <c r="S39" s="0">
-        <v>1.2213244172007049</v>
+        <v>1.221324417200705</v>
       </c>
       <c r="T39" s="0">
         <v>1.4409615515946175</v>
@@ -14023,13 +14024,13 @@
         <v>1.4420803782505898</v>
       </c>
       <c r="AD39" s="0">
-        <v>1.4513442778967391</v>
+        <v>1.4513442778967392</v>
       </c>
       <c r="AE39" s="0">
         <v>1.092896174863387</v>
       </c>
       <c r="AF39" s="0">
-        <v>1.684210526315788</v>
+        <v>1.6842105263157881</v>
       </c>
       <c r="AG39" s="0">
         <v>0.90538705296514177</v>
@@ -14260,7 +14261,7 @@
         <v>0.62537947783849368</v>
       </c>
       <c r="DE39" s="0">
-        <v>1.3855324633478316</v>
+        <v>1.3855324633478317</v>
       </c>
       <c r="DF39" s="0">
         <v>3.8684389911383743</v>
@@ -14334,7 +14335,7 @@
         <v>1.3141537915112758</v>
       </c>
       <c r="M40" s="0">
-        <v>1.2889812889812879</v>
+        <v>1.288981288981288</v>
       </c>
       <c r="N40" s="0">
         <v>1.2461059190031141</v>
@@ -14355,7 +14356,7 @@
         <v>1.3699266276585853</v>
       </c>
       <c r="T40" s="0">
-        <v>1.1746226866079343</v>
+        <v>1.1746226866079344</v>
       </c>
       <c r="U40" s="0">
         <v>0.89235917456776281</v>
@@ -14457,7 +14458,7 @@
         <v>1.0170913285100127</v>
       </c>
       <c r="BB40" s="0">
-        <v>1.0841711019120825</v>
+        <v>1.0841711019120826</v>
       </c>
       <c r="BC40" s="0">
         <v>0.63484002031488007</v>
@@ -14502,7 +14503,7 @@
         <v>1.4329805996472649</v>
       </c>
       <c r="BQ40" s="0">
-        <v>0.57430007178750841</v>
+        <v>0.57430007178750842</v>
       </c>
       <c r="BR40" s="0">
         <v>1.4692823121013954</v>
@@ -14705,7 +14706,7 @@
         <v>1.4435436029266351</v>
       </c>
       <c r="P41" s="0">
-        <v>1.1886481260308241</v>
+        <v>1.1886481260308242</v>
       </c>
       <c r="Q41" s="0">
         <v>1.1831275720164598</v>
@@ -14717,7 +14718,7 @@
         <v>1.179530045509426</v>
       </c>
       <c r="T41" s="0">
-        <v>1.2497439049375116</v>
+        <v>1.2497439049375117</v>
       </c>
       <c r="U41" s="0">
         <v>0.91094999070459104</v>
@@ -14741,7 +14742,7 @@
         <v>1.0847258868367038</v>
       </c>
       <c r="AB41" s="0">
-        <v>1.410177805027589</v>
+        <v>1.4101778050275891</v>
       </c>
       <c r="AC41" s="0">
         <v>1.1583924349881787</v>
@@ -14966,7 +14967,7 @@
         <v>0.73505912432086862</v>
       </c>
       <c r="CY41" s="0">
-        <v>0.72129021800794157</v>
+        <v>0.72129021800794158</v>
       </c>
       <c r="CZ41" s="0">
         <v>0.031072788005903802</v>
@@ -15061,7 +15062,7 @@
         <v>1.3167013167013155</v>
       </c>
       <c r="N42" s="0">
-        <v>1.3187954309449625</v>
+        <v>1.3187954309449626</v>
       </c>
       <c r="O42" s="0">
         <v>1.4501351262276698</v>
@@ -15079,7 +15080,7 @@
         <v>1.3652828085817765</v>
       </c>
       <c r="T42" s="0">
-        <v>1.2702315099364871</v>
+        <v>1.2702315099364872</v>
       </c>
       <c r="U42" s="0">
         <v>0.87376835843093437</v>
@@ -15094,7 +15095,7 @@
         <v>1.0422588592003021</v>
       </c>
       <c r="Y42" s="0">
-        <v>0.44549266247379415</v>
+        <v>0.44549266247379416</v>
       </c>
       <c r="Z42" s="0">
         <v>1.3498055364905046</v>
@@ -15136,7 +15137,7 @@
         <v>0.54813954988069846</v>
       </c>
       <c r="AM42" s="0">
-        <v>0.52517763361136804</v>
+        <v>0.52517763361136805</v>
       </c>
       <c r="AN42" s="0">
         <v>0.43459365493263763</v>
@@ -15226,7 +15227,7 @@
         <v>1.3594944150499693</v>
       </c>
       <c r="BQ42" s="0">
-        <v>0.35893754486719281</v>
+        <v>0.35893754486719282</v>
       </c>
       <c r="BR42" s="0">
         <v>1.4289174134172908</v>
@@ -15238,7 +15239,7 @@
         <v>0.94971593318069958</v>
       </c>
       <c r="BU42" s="0">
-        <v>1.4402652574862695</v>
+        <v>1.4402652574862696</v>
       </c>
       <c r="BV42" s="0">
         <v>1.1302211302211291</v>
@@ -15253,7 +15254,7 @@
         <v>1.3517279821627637</v>
       </c>
       <c r="BZ42" s="0">
-        <v>0.73723012111637642</v>
+        <v>0.73723012111637643</v>
       </c>
       <c r="CA42" s="0">
         <v>0.95238095238095155</v>
@@ -15349,7 +15350,7 @@
         <v>0.27388432415015285</v>
       </c>
       <c r="DF42" s="0">
-        <v>1.9256987048398075</v>
+        <v>1.9256987048398076</v>
       </c>
       <c r="DG42" s="0">
         <v>0</v>
@@ -15376,7 +15377,7 @@
         <v>0</v>
       </c>
       <c r="DO42" s="0">
-        <v>0.40453074433656921</v>
+        <v>0.40453074433656922</v>
       </c>
       <c r="DP42" s="0">
         <v>0</v>
@@ -15417,7 +15418,7 @@
         <v>1.2732801216267569</v>
       </c>
       <c r="L43" s="0">
-        <v>1.1188066062866266</v>
+        <v>1.1188066062866267</v>
       </c>
       <c r="M43" s="0">
         <v>1.2058212058212048</v>
@@ -15435,7 +15436,7 @@
         <v>1.2345679012345667</v>
       </c>
       <c r="R43" s="0">
-        <v>1.377410468319558</v>
+        <v>1.3774104683195581</v>
       </c>
       <c r="S43" s="0">
         <v>1.393145723042629</v>
@@ -15501,7 +15502,7 @@
         <v>0.49428483163422882</v>
       </c>
       <c r="AN43" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO43" s="0">
         <v>1.0337078651685383</v>
@@ -15603,7 +15604,7 @@
         <v>1.0465236763029728</v>
       </c>
       <c r="BV43" s="0">
-        <v>0.93366093366093283</v>
+        <v>0.93366093366093284</v>
       </c>
       <c r="BW43" s="0">
         <v>0.78947368421052566</v>
@@ -15636,7 +15637,7 @@
         <v>0.57570523891767367</v>
       </c>
       <c r="CG43" s="0">
-        <v>1.2940967913490506</v>
+        <v>1.2940967913490507</v>
       </c>
       <c r="CH43" s="0">
         <v>1.3161962810829897</v>
@@ -15818,7 +15819,7 @@
         <v>1.3075611142694701</v>
       </c>
       <c r="Y44" s="0">
-        <v>0.31446540880503115</v>
+        <v>0.31446540880503116</v>
       </c>
       <c r="Z44" s="0">
         <v>1.2125371768474023</v>
@@ -15932,7 +15933,7 @@
         <v>1.1166390270867872</v>
       </c>
       <c r="BK44" s="0">
-        <v>0.7761522082560609</v>
+        <v>0.77615220825606091</v>
       </c>
       <c r="BL44" s="0">
         <v>0.67507323907782379</v>
@@ -16043,7 +16044,7 @@
         <v>0</v>
       </c>
       <c r="CV44" s="0">
-        <v>0.87064676616915337</v>
+        <v>0.87064676616915338</v>
       </c>
       <c r="CW44" s="0">
         <v>0.012134449702705972</v>
@@ -16180,7 +16181,7 @@
         <v>1.269660792116732</v>
       </c>
       <c r="Y45" s="0">
-        <v>0.31446540880503115</v>
+        <v>0.31446540880503116</v>
       </c>
       <c r="Z45" s="0">
         <v>0.96087851750171505</v>
@@ -16333,7 +16334,7 @@
         <v>0.59941520467836207</v>
       </c>
       <c r="BX45" s="0">
-        <v>0.77128032534006385</v>
+        <v>0.77128032534006386</v>
       </c>
       <c r="BY45" s="0">
         <v>0.91973244147157107</v>
@@ -16500,7 +16501,7 @@
         <v>1.3875567491527681</v>
       </c>
       <c r="K46" s="0">
-        <v>0.85518814139111154</v>
+        <v>0.85518814139111155</v>
       </c>
       <c r="L46" s="0">
         <v>1.420706801633822</v>
@@ -16554,7 +16555,7 @@
         <v>1.0423053341508344</v>
       </c>
       <c r="AC46" s="0">
-        <v>0.87470449172577402</v>
+        <v>0.87470449172577403</v>
       </c>
       <c r="AD46" s="0">
         <v>0.73756840352129904</v>
@@ -16602,13 +16603,13 @@
         <v>1.2461059190031234</v>
       </c>
       <c r="AS46" s="0">
-        <v>0.79365079365079882</v>
+        <v>0.79365079365079883</v>
       </c>
       <c r="AT46" s="0">
         <v>0.1112966054535344</v>
       </c>
       <c r="AU46" s="0">
-        <v>0.2967359050445123</v>
+        <v>0.29673590504451231</v>
       </c>
       <c r="AV46" s="0">
         <v>0.39496236679335528</v>
@@ -16692,7 +16693,7 @@
         <v>0.68796068796069243</v>
       </c>
       <c r="BW46" s="0">
-        <v>0.76023391812865992</v>
+        <v>0.76023391812865993</v>
       </c>
       <c r="BX46" s="0">
         <v>0.49081475248913514</v>
@@ -16713,7 +16714,7 @@
         <v>0.26246719160105159</v>
       </c>
       <c r="CD46" s="0">
-        <v>1.3076923076923161</v>
+        <v>1.3076923076923162</v>
       </c>
       <c r="CE46" s="0">
         <v>0.57142857142857517</v>
@@ -16743,7 +16744,7 @@
         <v>1.3601639649711286</v>
       </c>
       <c r="CN46" s="0">
-        <v>0.56233548695860613</v>
+        <v>0.56233548695860614</v>
       </c>
       <c r="CO46" s="0">
         <v>1.3091774662787707</v>
@@ -16841,7 +16842,7 @@
         <v>1.1636470761525988</v>
       </c>
       <c r="D47" s="0">
-        <v>1.2867797721498226</v>
+        <v>1.2867797721498227</v>
       </c>
       <c r="E47" s="0">
         <v>1.1245054979285416</v>
@@ -16877,7 +16878,7 @@
         <v>1.0810098213697175</v>
       </c>
       <c r="P47" s="0">
-        <v>1.1886481260308241</v>
+        <v>1.1886481260308242</v>
       </c>
       <c r="Q47" s="0">
         <v>1.6975308641975293</v>
@@ -16889,7 +16890,7 @@
         <v>1.179530045509426</v>
       </c>
       <c r="T47" s="0">
-        <v>1.3453527282660644</v>
+        <v>1.3453527282660645</v>
       </c>
       <c r="U47" s="0">
         <v>0.39040713887339618</v>
@@ -17084,7 +17085,7 @@
         <v>0.74841681059297582</v>
       </c>
       <c r="CG47" s="0">
-        <v>1.2172782603557279</v>
+        <v>1.217278260355728</v>
       </c>
       <c r="CH47" s="0">
         <v>1.1881100658098129</v>
@@ -17311,7 +17312,7 @@
         <v>0.092678405931417893</v>
       </c>
       <c r="AN48" s="0">
-        <v>0.17383746197305502</v>
+        <v>0.17383746197305503</v>
       </c>
       <c r="AO48" s="0">
         <v>0.59925093632958748</v>
@@ -17338,7 +17339,7 @@
         <v>0.26827632461435258</v>
       </c>
       <c r="AW48" s="0">
-        <v>0.52027269465374903</v>
+        <v>0.52027269465374904</v>
       </c>
       <c r="AX48" s="0">
         <v>0.20257267294641934</v>
@@ -17353,7 +17354,7 @@
         <v>0.52427388067526426</v>
       </c>
       <c r="BB48" s="0">
-        <v>0.58150995466193522</v>
+        <v>0.58150995466193523</v>
       </c>
       <c r="BC48" s="0">
         <v>0.11850347045877761</v>
@@ -17619,7 +17620,7 @@
         <v>0.26027142591559749</v>
       </c>
       <c r="V49" s="0">
-        <v>0.68933823529411697</v>
+        <v>0.68933823529411698</v>
       </c>
       <c r="W49" s="0">
         <v>0.17094017094017078</v>
@@ -17658,7 +17659,7 @@
         <v>0.51538217570567668</v>
       </c>
       <c r="AI49" s="0">
-        <v>0.43579608797000063</v>
+        <v>0.43579608797000064</v>
       </c>
       <c r="AJ49" s="0">
         <v>0.70175438596491169</v>
@@ -17981,7 +17982,7 @@
         <v>0.29745305818925427</v>
       </c>
       <c r="V50" s="0">
-        <v>0.61274509803921517</v>
+        <v>0.61274509803921518</v>
       </c>
       <c r="W50" s="0">
         <v>0.30769230769230743</v>
@@ -18490,7 +18491,7 @@
         <v>0.56510858157745969</v>
       </c>
       <c r="BS51" s="0">
-        <v>0.27868653822852268</v>
+        <v>0.27868653822852269</v>
       </c>
       <c r="BT51" s="0">
         <v>0.29254642584584051</v>
@@ -18541,7 +18542,7 @@
         <v>0.39933444259567352</v>
       </c>
       <c r="CJ51" s="0">
-        <v>0.031625553447185296</v>
+        <v>0.031625553447185297</v>
       </c>
       <c r="CK51" s="0">
         <v>0.31502767134951015</v>
@@ -18654,13 +18655,13 @@
         <v>1.0572903860339309</v>
       </c>
       <c r="E52" s="0">
-        <v>0.65102949880073457</v>
+        <v>0.65102949880073458</v>
       </c>
       <c r="F52" s="0">
         <v>1.0903560873432603</v>
       </c>
       <c r="G52" s="0">
-        <v>0.85470085470085388</v>
+        <v>0.85470085470085389</v>
       </c>
       <c r="H52" s="0">
         <v>0.8880815420324949</v>
@@ -18708,7 +18709,7 @@
         <v>0.41360294117647017</v>
       </c>
       <c r="W52" s="0">
-        <v>0.20512820512820495</v>
+        <v>0.20512820512820496</v>
       </c>
       <c r="X52" s="0">
         <v>1.0422588592003021</v>
@@ -18810,7 +18811,7 @@
         <v>0.67146282973621041</v>
       </c>
       <c r="BE52" s="0">
-        <v>0.20315674324113125</v>
+        <v>0.20315674324113126</v>
       </c>
       <c r="BF52" s="0">
         <v>0.33319450229071196</v>
@@ -18849,7 +18850,7 @@
         <v>0.083752093802344982</v>
       </c>
       <c r="BR52" s="0">
-        <v>0.42786792605150525</v>
+        <v>0.42786792605150526</v>
       </c>
       <c r="BS52" s="0">
         <v>0.21002463750555334</v>
@@ -18915,7 +18916,7 @@
         <v>0.85708962176262271</v>
       </c>
       <c r="CN52" s="0">
-        <v>0.35893754486719281</v>
+        <v>0.35893754486719282</v>
       </c>
       <c r="CO52" s="0">
         <v>0.9212730318257949</v>
@@ -19019,7 +19020,7 @@
         <v>0.67906426190698632</v>
       </c>
       <c r="F53" s="0">
-        <v>0.9497575392384715</v>
+        <v>0.94975753923847151</v>
       </c>
       <c r="G53" s="0">
         <v>0.6143162393162388</v>
@@ -19187,19 +19188,19 @@
         <v>0.17930787161556375</v>
       </c>
       <c r="BJ53" s="0">
-        <v>0.59332964805601573</v>
+        <v>0.59332964805601574</v>
       </c>
       <c r="BK53" s="0">
         <v>0.17171509032213736</v>
       </c>
       <c r="BL53" s="0">
-        <v>0.18468984842695182</v>
+        <v>0.18468984842695183</v>
       </c>
       <c r="BM53" s="0">
         <v>0.62576047279680114</v>
       </c>
       <c r="BN53" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO53" s="0">
         <v>0.41652594844084168</v>
@@ -19262,7 +19263,7 @@
         <v>0.93193763526345919</v>
       </c>
       <c r="CI53" s="0">
-        <v>0.26622296173044901</v>
+        <v>0.26622296173044902</v>
       </c>
       <c r="CJ53" s="0">
         <v>0.021083702298123532</v>
@@ -19423,7 +19424,7 @@
         <v>0.82195597659515118</v>
       </c>
       <c r="T54" s="0">
-        <v>0.69657856996517042</v>
+        <v>0.69657856996517043</v>
       </c>
       <c r="U54" s="0">
         <v>0.074363264547313568</v>
@@ -19525,7 +19526,7 @@
         <v>0.34602076124567444</v>
       </c>
       <c r="BB54" s="0">
-        <v>0.23654642223536348</v>
+        <v>0.23654642223536349</v>
       </c>
       <c r="BC54" s="0">
         <v>0.021161334010496004</v>
@@ -19576,7 +19577,7 @@
         <v>0.35521110842011755</v>
       </c>
       <c r="BS54" s="0">
-        <v>0.17367421947574604</v>
+        <v>0.17367421947574605</v>
       </c>
       <c r="BT54" s="0">
         <v>0.13567370474009993</v>
@@ -19869,7 +19870,7 @@
         <v>0.037091988130564038</v>
       </c>
       <c r="AV55" s="0">
-        <v>0.067069081153588644</v>
+        <v>0.067069081153588645</v>
       </c>
       <c r="AW55" s="0">
         <v>0.14352350197344907</v>
@@ -19956,7 +19957,7 @@
         <v>0.12620950778292048</v>
       </c>
       <c r="BY55" s="0">
-        <v>0.26477146042363608</v>
+        <v>0.26477146042363609</v>
       </c>
       <c r="BZ55" s="0">
         <v>0.052659294365455848</v>
@@ -20093,7 +20094,7 @@
         <v>0.43875538381032847</v>
       </c>
       <c r="B56" s="0">
-        <v>0.80699113564141089</v>
+        <v>0.8069911356414109</v>
       </c>
       <c r="C56" s="0">
         <v>0.53321549565473514</v>
@@ -20132,7 +20133,7 @@
         <v>0.60228452751817185</v>
       </c>
       <c r="O56" s="0">
-        <v>0.62619471359831202</v>
+        <v>0.62619471359831203</v>
       </c>
       <c r="P56" s="0">
         <v>0.56873116078029862</v>
@@ -20273,7 +20274,7 @@
         <v>0.11117088040164953</v>
       </c>
       <c r="BJ56" s="0">
-        <v>0.3095632946379212</v>
+        <v>0.30956329463792121</v>
       </c>
       <c r="BK56" s="0">
         <v>0.089291846967511412</v>
@@ -20291,7 +20292,7 @@
         <v>0.22514916131937388</v>
       </c>
       <c r="BP56" s="0">
-        <v>0.27189888300999387</v>
+        <v>0.27189888300999388</v>
       </c>
       <c r="BQ56" s="0">
         <v>0.011964584828906426</v>
@@ -20330,7 +20331,7 @@
         <v>0.2099737532808397</v>
       </c>
       <c r="CC56" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD56" s="0">
         <v>0.41025641025640991</v>
@@ -20455,7 +20456,7 @@
         <v>0.43875538381032847</v>
       </c>
       <c r="B57" s="0">
-        <v>0.62719518314099298</v>
+        <v>0.62719518314099299</v>
       </c>
       <c r="C57" s="0">
         <v>0.43305346884666335</v>
@@ -20518,7 +20519,7 @@
         <v>0.26041666666666646</v>
       </c>
       <c r="W57" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X57" s="0">
         <v>0.54955467121470492</v>
@@ -20707,7 +20708,7 @@
         <v>0.40182000827276454</v>
       </c>
       <c r="CH57" s="0">
-        <v>0.61834724614637115</v>
+        <v>0.61834724614637116</v>
       </c>
       <c r="CI57" s="0">
         <v>0.14420410427065988</v>
@@ -20820,7 +20821,7 @@
         <v>0.51011874895467424</v>
       </c>
       <c r="C58" s="0">
-        <v>0.38297245544262742</v>
+        <v>0.38297245544262743</v>
       </c>
       <c r="D58" s="0">
         <v>0.5163511187607569</v>
@@ -20901,7 +20902,7 @@
         <v>0.28368794326241109</v>
       </c>
       <c r="AD58" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE58" s="0">
         <v>0.20491803278688506</v>
@@ -20982,7 +20983,7 @@
         <v>0.23980815347721801</v>
       </c>
       <c r="BE58" s="0">
-        <v>0.031254883575558653</v>
+        <v>0.031254883575558654</v>
       </c>
       <c r="BF58" s="0">
         <v>0.12494793835901696</v>
@@ -21027,7 +21028,7 @@
         <v>0.068661900722969363</v>
       </c>
       <c r="BT58" s="0">
-        <v>0.072076655643178097</v>
+        <v>0.072076655643178098</v>
       </c>
       <c r="BU58" s="0">
         <v>0.46627292508548296</v>
@@ -21045,7 +21046,7 @@
         <v>0.11148272017837225</v>
       </c>
       <c r="BZ58" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA58" s="0">
         <v>0.15037593984962394</v>
@@ -21054,7 +21055,7 @@
         <v>0.10498687664041985</v>
       </c>
       <c r="CC58" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD58" s="0">
         <v>0.24358974358974336</v>
@@ -21075,7 +21076,7 @@
         <v>0.088740987243483005</v>
       </c>
       <c r="CJ58" s="0">
-        <v>0.031625553447185296</v>
+        <v>0.031625553447185297</v>
       </c>
       <c r="CK58" s="0">
         <v>0.085142613878245996</v>
@@ -21209,7 +21210,7 @@
         <v>0.11402508551881405</v>
       </c>
       <c r="L59" s="0">
-        <v>0.58604155567394733</v>
+        <v>0.58604155567394734</v>
       </c>
       <c r="M59" s="0">
         <v>0.22176022176022159</v>
@@ -21263,7 +21264,7 @@
         <v>0.23640661938534258</v>
       </c>
       <c r="AD59" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE59" s="0">
         <v>0.27322404371584674</v>
@@ -21368,7 +21369,7 @@
         <v>0.050948923703986709</v>
       </c>
       <c r="BM59" s="0">
-        <v>0.15644011819920028</v>
+        <v>0.15644011819920029</v>
       </c>
       <c r="BN59" s="0">
         <v>0.010348752975266471</v>
@@ -21407,7 +21408,7 @@
         <v>0.097547380156075711</v>
       </c>
       <c r="BZ59" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA59" s="0">
         <v>0</v>
@@ -21437,7 +21438,7 @@
         <v>0.12201885745978913</v>
       </c>
       <c r="CJ59" s="0">
-        <v>0.031625553447185296</v>
+        <v>0.031625553447185297</v>
       </c>
       <c r="CK59" s="0">
         <v>0.068114091102596794</v>
@@ -21718,7 +21719,7 @@
         <v>0.10597947344935288</v>
       </c>
       <c r="BI60" s="0">
-        <v>0.032275416890801475</v>
+        <v>0.032275416890801476</v>
       </c>
       <c r="BJ60" s="0">
         <v>0.22848719366132281</v>
@@ -21769,7 +21770,7 @@
         <v>0.097547380156075711</v>
       </c>
       <c r="BZ60" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA60" s="0">
         <v>0.10025062656641595</v>
@@ -21906,7 +21907,7 @@
         <v>0.37213580866365581</v>
       </c>
       <c r="C61" s="0">
-        <v>0.23272941523051976</v>
+        <v>0.23272941523051977</v>
       </c>
       <c r="D61" s="0">
         <v>0.28959374914624458</v>
@@ -21969,7 +21970,7 @@
         <v>0.034188034188034157</v>
       </c>
       <c r="X61" s="0">
-        <v>0.36005306045101348</v>
+        <v>0.36005306045101349</v>
       </c>
       <c r="Y61" s="0">
         <v>0</v>
@@ -22041,7 +22042,7 @@
         <v>0.012363996043521256</v>
       </c>
       <c r="AV61" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW61" s="0">
         <v>0.017940437746681002</v>
@@ -22116,7 +22117,7 @@
         <v>0.033918426185024983</v>
       </c>
       <c r="BU61" s="0">
-        <v>0.15542430836182763</v>
+        <v>0.15542430836182764</v>
       </c>
       <c r="BV61" s="0">
         <v>0.11466011466011455</v>
@@ -22131,13 +22132,13 @@
         <v>0.11148272017837225</v>
       </c>
       <c r="BZ61" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA61" s="0">
         <v>0</v>
       </c>
       <c r="CB61" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC61" s="0">
         <v>0</v>
@@ -22304,7 +22305,7 @@
         <v>0.2699896157840081</v>
       </c>
       <c r="O62" s="0">
-        <v>0.21092874563311564</v>
+        <v>0.21092874563311565</v>
       </c>
       <c r="P62" s="0">
         <v>0.2161178410965135</v>
@@ -22439,7 +22440,7 @@
         <v>0.024645717806531093</v>
       </c>
       <c r="BH62" s="0">
-        <v>0.066934404283801804</v>
+        <v>0.066934404283801805</v>
       </c>
       <c r="BI62" s="0">
         <v>0.0035861574323112753</v>
@@ -22499,7 +22500,7 @@
         <v>0.050125313283207976</v>
       </c>
       <c r="CB62" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC62" s="0">
         <v>0.012498437695288078</v>
@@ -22657,13 +22658,13 @@
         <v>0.15203344735841984</v>
       </c>
       <c r="L63" s="0">
-        <v>0.19534718522465055</v>
+        <v>0.19534718522465056</v>
       </c>
       <c r="M63" s="0">
         <v>0.13860013860013951</v>
       </c>
       <c r="N63" s="0">
-        <v>0.15576323987539042</v>
+        <v>0.15576323987539043</v>
       </c>
       <c r="O63" s="0">
         <v>0.13842198932173316</v>
@@ -22834,7 +22835,7 @@
         <v>0.056510858157746389</v>
       </c>
       <c r="BS63" s="0">
-        <v>0.012116806009935858</v>
+        <v>0.012116806009935859</v>
       </c>
       <c r="BT63" s="0">
         <v>0.0084796065462563082</v>
@@ -22995,7 +22996,7 @@
         <v>0.12372956252761809</v>
       </c>
       <c r="D64" s="0">
-        <v>0.20763325410485461</v>
+        <v>0.20763325410485462</v>
       </c>
       <c r="E64" s="0">
         <v>0.087219262997227584</v>
@@ -23127,7 +23128,7 @@
         <v>0</v>
       </c>
       <c r="AV64" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW64" s="0">
         <v>0.026910656620021504</v>
@@ -23202,7 +23203,7 @@
         <v>0.029678622911896862</v>
       </c>
       <c r="BU64" s="0">
-        <v>0.15542430836182763</v>
+        <v>0.15542430836182764</v>
       </c>
       <c r="BV64" s="0">
         <v>0.049140049140049095</v>
@@ -23513,7 +23514,7 @@
         <v>0</v>
       </c>
       <c r="BD65" s="0">
-        <v>0.054813292223364118</v>
+        <v>0.054813292223364119</v>
       </c>
       <c r="BE65" s="0">
         <v>0</v>
@@ -23540,7 +23541,7 @@
         <v>0.012737230925996677</v>
       </c>
       <c r="BM65" s="0">
-        <v>0.081117098325511255</v>
+        <v>0.081117098325511256</v>
       </c>
       <c r="BN65" s="0">
         <v>0</v>
@@ -23585,7 +23586,7 @@
         <v>0.050125313283207976</v>
       </c>
       <c r="CB65" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC65" s="0">
         <v>0.012498437695288078</v>
@@ -24177,7 +24178,7 @@
         <v>0</v>
       </c>
       <c r="AJ67" s="0">
-        <v>0.030959752321981625</v>
+        <v>0.030959752321981626</v>
       </c>
       <c r="AK67" s="0">
         <v>0.052002080083203665</v>
@@ -24282,7 +24283,7 @@
         <v>0.03229191894728365</v>
       </c>
       <c r="BS67" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT67" s="0">
         <v>0.0042398032731281541</v>
@@ -24635,7 +24636,7 @@
         <v>0</v>
       </c>
       <c r="BP68" s="0">
-        <v>0.022045855379188527</v>
+        <v>0.022045855379188528</v>
       </c>
       <c r="BQ68" s="0">
         <v>0</v>
@@ -24686,7 +24687,7 @@
         <v>0</v>
       </c>
       <c r="CG68" s="0">
-        <v>0.04136382438101957</v>
+        <v>0.041363824381019571</v>
       </c>
       <c r="CH68" s="0">
         <v>0.088335320878052348</v>
@@ -24988,7 +24989,7 @@
         <v>0.012737230925996771</v>
       </c>
       <c r="BM69" s="0">
-        <v>0.017382235355466825</v>
+        <v>0.017382235355466826</v>
       </c>
       <c r="BN69" s="0">
         <v>0</v>
@@ -25565,7 +25566,7 @@
         <v>0.046140663107244385</v>
       </c>
       <c r="P71" s="0">
-        <v>0.0056873116078030288</v>
+        <v>0.0056873116078030289</v>
       </c>
       <c r="Q71" s="0">
         <v>0.051440329218107331</v>
@@ -25730,7 +25731,7 @@
         <v>0</v>
       </c>
       <c r="BS71" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT71" s="0">
         <v>0.0042398032731281541</v>
@@ -25885,7 +25886,7 @@
         <v>0.008050557501106885</v>
       </c>
       <c r="B72" s="0">
-        <v>0.020906506104699608</v>
+        <v>0.020906506104699609</v>
       </c>
       <c r="C72" s="0">
         <v>0.014729709824716332</v>
@@ -25915,7 +25916,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="0">
-        <v>0.017758835020422511</v>
+        <v>0.017758835020422512</v>
       </c>
       <c r="M72" s="0">
         <v>0</v>
@@ -26244,7 +26245,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.016101115002214009</v>
+        <v>0.01610111500221401</v>
       </c>
       <c r="B73" s="0">
         <v>0.041813012209399834</v>
@@ -26268,7 +26269,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="0">
-        <v>0.038759689922480869</v>
+        <v>0.03875968992248087</v>
       </c>
       <c r="J73" s="0">
         <v>0.031971353667114476</v>
@@ -26627,7 +26628,7 @@
         <v>0</v>
       </c>
       <c r="H74" s="0">
-        <v>0.020183671409829278</v>
+        <v>0.020183671409829279</v>
       </c>
       <c r="I74" s="0">
         <v>0.033222591362125964</v>
@@ -27013,7 +27014,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="0">
-        <v>0.0056873116078030288</v>
+        <v>0.0056873116078030289</v>
       </c>
       <c r="Q75" s="0">
         <v>0</v>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0006_ses-01_pet_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0006_ses-01_pet_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
